--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.38680197056439</v>
+        <v>12.41285532021671</v>
       </c>
       <c r="D2" t="n">
-        <v>46.90872049048051</v>
+        <v>7.622667079703083</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80359201659942</v>
+        <v>1.918083702697405</v>
       </c>
       <c r="F2" t="n">
-        <v>10.42148761180305</v>
+        <v>1.693491736917995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.40952029825593</v>
+        <v>7.86654704846659</v>
       </c>
       <c r="D3" t="n">
-        <v>48.50854582673333</v>
+        <v>7.882638696844166</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80359201659942</v>
+        <v>1.918083702697405</v>
       </c>
       <c r="F3" t="n">
-        <v>10.42148761180305</v>
+        <v>1.693491736917995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.71601780386047</v>
+        <v>11.16635289312733</v>
       </c>
       <c r="D4" t="n">
-        <v>25.64477725435817</v>
+        <v>4.167276303833203</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80359201659942</v>
+        <v>1.918083702697405</v>
       </c>
       <c r="F4" t="n">
-        <v>10.42148761180305</v>
+        <v>1.693491736917995</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
